--- a/departures.xlsx
+++ b/departures.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\christianli\interamerica.org Dropbox\Elizabeth Christian\- 2026\Secretaries Academy  August 2-5, 2026\Transportation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RomeroJo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90C2A987-6AB6-4AF1-8039-1F35CBB87442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95B843CE-7F5A-4DAA-8C9E-585ADB093D11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25320" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DEPARTURE  SCHEDULE" sheetId="12" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="84">
   <si>
     <t>Union</t>
   </si>
@@ -648,10 +648,6 @@
     <dxf>
       <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
@@ -660,6 +656,7 @@
       </border>
     </dxf>
     <dxf>
+      <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -709,6 +706,9 @@
         </top>
         <bottom/>
       </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -801,8 +801,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table159" displayName="Table159" ref="E1:G25" totalsRowCount="1" headerRowDxfId="15" dataDxfId="14">
-  <autoFilter ref="E1:G24" xr:uid="{00000000-0009-0000-0100-000008000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table159" displayName="Table159" ref="E1:G13" totalsRowCount="1" headerRowDxfId="15" dataDxfId="14">
+  <autoFilter ref="E1:G12" xr:uid="{00000000-0009-0000-0100-000008000000}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Union" dataDxfId="13" totalsRowDxfId="12"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="PAX" dataDxfId="11" totalsRowDxfId="10"/>
@@ -816,9 +816,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F3FCDB54-2A6F-4023-A14D-5EF7409883B5}" name="Table1592" displayName="Table1592" ref="E1:G15" totalsRowCount="1" headerRowDxfId="7" dataDxfId="6">
   <autoFilter ref="E1:G14" xr:uid="{00000000-0009-0000-0100-000008000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{0FDFDE3C-1B85-4522-8E3F-0D77D4699A01}" name="Union" dataDxfId="4" totalsRowDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{F27CF665-795F-4498-B84E-10109FCE4642}" name="PAX" dataDxfId="2" totalsRowDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{90A603DE-F9B0-49B9-A77D-8011DF1BA239}" name="AIRLINE" dataDxfId="0" totalsRowDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{0FDFDE3C-1B85-4522-8E3F-0D77D4699A01}" name="Union" dataDxfId="5" totalsRowDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{F27CF665-795F-4498-B84E-10109FCE4642}" name="PAX" dataDxfId="3" totalsRowDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{90A603DE-F9B0-49B9-A77D-8011DF1BA239}" name="AIRLINE" dataDxfId="1" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1317,7 +1317,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -1570,252 +1570,22 @@
       <c r="F11" s="1"/>
       <c r="G11" s="29"/>
     </row>
-    <row r="12" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="6"/>
-      <c r="B12" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="C12" s="20"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="27"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="1"/>
       <c r="F12" s="1"/>
-      <c r="G12" s="29"/>
-    </row>
-    <row r="13" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
-        <v>46240</v>
-      </c>
-      <c r="B13" s="23">
-        <v>0.26666666666666666</v>
-      </c>
-      <c r="C13" s="20">
-        <v>246</v>
-      </c>
-      <c r="D13" s="24" t="s">
-        <v>60</v>
-      </c>
-      <c r="E13" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="F13" s="1">
-        <v>2</v>
-      </c>
-      <c r="G13" s="29" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="4">
-        <v>46240</v>
-      </c>
-      <c r="B14" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" s="20">
-        <v>200</v>
-      </c>
-      <c r="D14" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="E14" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="F14" s="1">
-        <v>1</v>
-      </c>
-      <c r="G14" s="29" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="4">
-        <v>46240</v>
-      </c>
-      <c r="B15" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="E15" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="F15" s="1">
-        <v>2</v>
-      </c>
-      <c r="G15" s="24" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="4">
-        <v>46240</v>
-      </c>
-      <c r="B16" s="23">
-        <v>0.55763888888888891</v>
-      </c>
-      <c r="C16" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" s="25" t="s">
-        <v>59</v>
-      </c>
-      <c r="E16" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="F16" s="1">
-        <v>1</v>
-      </c>
-      <c r="G16" s="24" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="4">
-        <v>46240</v>
-      </c>
-      <c r="B17" s="23">
-        <v>0.56944444444444442</v>
-      </c>
-      <c r="C17" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="E17" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" s="1">
-        <v>1</v>
-      </c>
-      <c r="G17" s="24" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="4">
-        <v>46240</v>
-      </c>
-      <c r="B18" s="23">
-        <v>0.73888888888888893</v>
-      </c>
-      <c r="C18" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="D18" s="24" t="s">
-        <v>63</v>
-      </c>
-      <c r="E18" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="F18" s="1">
-        <v>1</v>
-      </c>
-      <c r="G18" s="24" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="4">
-        <v>46240</v>
-      </c>
-      <c r="B19" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" s="22">
-        <v>2739</v>
-      </c>
-      <c r="D19" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="E19" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" s="1">
-        <v>1</v>
-      </c>
-      <c r="G19" s="24" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="6"/>
-      <c r="B20" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" s="20"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="29"/>
-    </row>
-    <row r="21" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="6"/>
-      <c r="B21" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="C21" s="20"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="22"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="29"/>
-    </row>
-    <row r="22" spans="1:7" ht="18" x14ac:dyDescent="0.25">
-      <c r="A22" s="6"/>
-      <c r="B22" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="C22" s="20"/>
-      <c r="D22" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="E22" s="27"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="29"/>
-    </row>
-    <row r="23" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="4">
-        <v>46240</v>
-      </c>
-      <c r="B23" s="23">
-        <v>0.51736111111111105</v>
-      </c>
-      <c r="C23" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="D23" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="E23" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="F23" s="1">
-        <v>1</v>
-      </c>
-      <c r="G23" s="24" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="6"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="3"/>
-    </row>
-    <row r="25" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="D25" s="10" t="s">
+      <c r="G12" s="3"/>
+    </row>
+    <row r="13" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="D13" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="E25" s="30"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="3"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
